--- a/INSTANCES/instances_xlsx/A_MTN_5/273FL_10A_3.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/273FL_10A_3.xlsx
@@ -8960,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -8994,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -9045,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -9079,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
